--- a/research/traditional_assets/database/data/denmark/denmark_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_auto_parts.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.274</v>
+        <v>-0.588</v>
       </c>
       <c r="G2">
-        <v>0.1023673469387755</v>
+        <v>-2.4296875</v>
       </c>
       <c r="H2">
-        <v>0.02481632653061224</v>
+        <v>-2.4296875</v>
       </c>
       <c r="I2">
-        <v>-0.2089795918367347</v>
+        <v>-1.625</v>
       </c>
       <c r="J2">
-        <v>-0.2089795918367347</v>
+        <v>-1.625</v>
       </c>
       <c r="K2">
-        <v>-4.46</v>
+        <v>-22.2</v>
       </c>
       <c r="L2">
-        <v>-0.1820408163265306</v>
+        <v>-17.34375</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -636,67 +636,67 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.2055299539170507</v>
+        <v>-1.947368421052631</v>
       </c>
       <c r="X2">
-        <v>0.1405588268380603</v>
+        <v>0.5899105586129674</v>
       </c>
       <c r="Y2">
-        <v>0.06497112707899044</v>
+        <v>-2.537278979665599</v>
       </c>
       <c r="Z2">
-        <v>0.4478157558033267</v>
+        <v>0.05981308411214954</v>
       </c>
       <c r="AA2">
-        <v>-0.09358435386583806</v>
+        <v>-0.097196261682243</v>
       </c>
       <c r="AB2">
-        <v>0.06898139651274351</v>
+        <v>0.1039466996396263</v>
       </c>
       <c r="AC2">
-        <v>-0.1625657503785816</v>
+        <v>-0.2011429613218693</v>
       </c>
       <c r="AD2">
-        <v>10</v>
+        <v>24.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10</v>
+        <v>24.2</v>
       </c>
       <c r="AG2">
-        <v>10</v>
+        <v>24.2</v>
       </c>
       <c r="AH2">
-        <v>0.6027727546714888</v>
+        <v>0.8883994126284875</v>
       </c>
       <c r="AI2">
-        <v>0.4672897196261683</v>
+        <v>2</v>
       </c>
       <c r="AJ2">
-        <v>0.6027727546714888</v>
+        <v>0.8883994126284875</v>
       </c>
       <c r="AK2">
-        <v>0.4672897196261683</v>
+        <v>2</v>
       </c>
       <c r="AL2">
-        <v>1.48</v>
+        <v>0.028</v>
       </c>
       <c r="AM2">
-        <v>1.48</v>
+        <v>0.014</v>
       </c>
       <c r="AN2">
-        <v>-1.626016260162602</v>
+        <v>-10.56768558951965</v>
       </c>
       <c r="AO2">
-        <v>-3.45945945945946</v>
+        <v>-74.28571428571429</v>
       </c>
       <c r="AP2">
-        <v>-1.626016260162602</v>
+        <v>-10.56768558951965</v>
       </c>
       <c r="AQ2">
-        <v>-3.45945945945946</v>
+        <v>-148.5714285714286</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.274</v>
+        <v>-0.588</v>
       </c>
       <c r="G3">
-        <v>0.1023673469387755</v>
+        <v>-2.4296875</v>
       </c>
       <c r="H3">
-        <v>0.02481632653061224</v>
+        <v>-2.4296875</v>
       </c>
       <c r="I3">
-        <v>-0.2089795918367347</v>
+        <v>-1.625</v>
       </c>
       <c r="J3">
-        <v>-0.2089795918367347</v>
+        <v>-1.625</v>
       </c>
       <c r="K3">
-        <v>-4.46</v>
+        <v>-22.2</v>
       </c>
       <c r="L3">
-        <v>-0.1820408163265306</v>
+        <v>-17.34375</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,67 +764,67 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.2055299539170507</v>
+        <v>-1.947368421052631</v>
       </c>
       <c r="X3">
-        <v>0.1405588268380603</v>
+        <v>0.5899105586129674</v>
       </c>
       <c r="Y3">
-        <v>0.06497112707899044</v>
+        <v>-2.537278979665599</v>
       </c>
       <c r="Z3">
-        <v>0.4478157558033267</v>
+        <v>0.05981308411214954</v>
       </c>
       <c r="AA3">
-        <v>-0.09358435386583806</v>
+        <v>-0.097196261682243</v>
       </c>
       <c r="AB3">
-        <v>0.06898139651274351</v>
+        <v>0.1039466996396263</v>
       </c>
       <c r="AC3">
-        <v>-0.1625657503785816</v>
+        <v>-0.2011429613218693</v>
       </c>
       <c r="AD3">
-        <v>10</v>
+        <v>24.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>10</v>
+        <v>24.2</v>
       </c>
       <c r="AG3">
-        <v>10</v>
+        <v>24.2</v>
       </c>
       <c r="AH3">
-        <v>0.6027727546714888</v>
+        <v>0.8883994126284875</v>
       </c>
       <c r="AI3">
-        <v>0.4672897196261683</v>
+        <v>2</v>
       </c>
       <c r="AJ3">
-        <v>0.6027727546714888</v>
+        <v>0.8883994126284875</v>
       </c>
       <c r="AK3">
-        <v>0.4672897196261683</v>
+        <v>2</v>
       </c>
       <c r="AL3">
-        <v>1.48</v>
+        <v>0.028</v>
       </c>
       <c r="AM3">
-        <v>1.48</v>
+        <v>0.014</v>
       </c>
       <c r="AN3">
-        <v>-1.626016260162602</v>
+        <v>-10.56768558951965</v>
       </c>
       <c r="AO3">
-        <v>-3.45945945945946</v>
+        <v>-74.28571428571429</v>
       </c>
       <c r="AP3">
-        <v>-1.626016260162602</v>
+        <v>-10.56768558951965</v>
       </c>
       <c r="AQ3">
-        <v>-3.45945945945946</v>
+        <v>-148.5714285714286</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_auto_parts.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_auto_parts.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.588</v>
+        <v>-0.664</v>
+      </c>
+      <c r="E2">
+        <v>0.424</v>
       </c>
       <c r="G2">
-        <v>-2.4296875</v>
+        <v>-4.272727272727272</v>
       </c>
       <c r="H2">
-        <v>-2.4296875</v>
+        <v>-4.272727272727272</v>
       </c>
       <c r="I2">
-        <v>-1.625</v>
+        <v>-3.090909090909091</v>
       </c>
       <c r="J2">
-        <v>-1.625</v>
+        <v>-3.090909090909091</v>
       </c>
       <c r="K2">
-        <v>-22.2</v>
+        <v>18.8</v>
       </c>
       <c r="L2">
-        <v>-17.34375</v>
+        <v>42.72727272727273</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,7 +627,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +639,61 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>-1.947368421052631</v>
+        <v>-1.553719008264463</v>
       </c>
       <c r="X2">
-        <v>0.5899105586129674</v>
+        <v>0.2737550112751288</v>
       </c>
       <c r="Y2">
-        <v>-2.537278979665599</v>
+        <v>-1.827474019539592</v>
       </c>
       <c r="Z2">
-        <v>0.05981308411214954</v>
+        <v>0.03636363636363636</v>
       </c>
       <c r="AA2">
-        <v>-0.097196261682243</v>
+        <v>-0.112396694214876</v>
       </c>
       <c r="AB2">
-        <v>0.1039466996396263</v>
+        <v>0.08622588761824887</v>
       </c>
       <c r="AC2">
-        <v>-0.2011429613218693</v>
+        <v>-0.1986225818331249</v>
       </c>
       <c r="AD2">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="AG2">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="AH2">
-        <v>0.8883994126284875</v>
+        <v>0.8082932692307692</v>
       </c>
       <c r="AI2">
-        <v>2</v>
+        <v>0.8129344212753098</v>
       </c>
       <c r="AJ2">
-        <v>0.8883994126284875</v>
+        <v>0.8082932692307692</v>
       </c>
       <c r="AK2">
-        <v>2</v>
+        <v>0.8129344212753098</v>
       </c>
       <c r="AL2">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="AM2">
-        <v>0.014</v>
-      </c>
-      <c r="AN2">
-        <v>-10.56768558951965</v>
+        <v>0.029</v>
       </c>
       <c r="AO2">
-        <v>-74.28571428571429</v>
-      </c>
-      <c r="AP2">
-        <v>-10.56768558951965</v>
+        <v>-46.89655172413793</v>
       </c>
       <c r="AQ2">
-        <v>-148.5714285714286</v>
+        <v>-46.89655172413793</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +713,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.588</v>
+        <v>-0.664</v>
+      </c>
+      <c r="E3">
+        <v>0.424</v>
       </c>
       <c r="G3">
-        <v>-2.4296875</v>
+        <v>-4.272727272727272</v>
       </c>
       <c r="H3">
-        <v>-2.4296875</v>
+        <v>-4.272727272727272</v>
       </c>
       <c r="I3">
-        <v>-1.625</v>
+        <v>-3.090909090909091</v>
       </c>
       <c r="J3">
-        <v>-1.625</v>
+        <v>-3.090909090909091</v>
       </c>
       <c r="K3">
-        <v>-22.2</v>
+        <v>18.8</v>
       </c>
       <c r="L3">
-        <v>-17.34375</v>
+        <v>42.72727272727273</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +743,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,7 +752,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +764,61 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>-1.947368421052631</v>
+        <v>-1.553719008264463</v>
       </c>
       <c r="X3">
-        <v>0.5899105586129674</v>
+        <v>0.2737550112751288</v>
       </c>
       <c r="Y3">
-        <v>-2.537278979665599</v>
+        <v>-1.827474019539592</v>
       </c>
       <c r="Z3">
-        <v>0.05981308411214954</v>
+        <v>0.03636363636363636</v>
       </c>
       <c r="AA3">
-        <v>-0.097196261682243</v>
+        <v>-0.112396694214876</v>
       </c>
       <c r="AB3">
-        <v>0.1039466996396263</v>
+        <v>0.08622588761824887</v>
       </c>
       <c r="AC3">
-        <v>-0.2011429613218693</v>
+        <v>-0.1986225818331249</v>
       </c>
       <c r="AD3">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="AG3">
-        <v>24.2</v>
+        <v>26.9</v>
       </c>
       <c r="AH3">
-        <v>0.8883994126284875</v>
+        <v>0.8082932692307692</v>
       </c>
       <c r="AI3">
-        <v>2</v>
+        <v>0.8129344212753098</v>
       </c>
       <c r="AJ3">
-        <v>0.8883994126284875</v>
+        <v>0.8082932692307692</v>
       </c>
       <c r="AK3">
-        <v>2</v>
+        <v>0.8129344212753098</v>
       </c>
       <c r="AL3">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="AM3">
-        <v>0.014</v>
-      </c>
-      <c r="AN3">
-        <v>-10.56768558951965</v>
+        <v>0.029</v>
       </c>
       <c r="AO3">
-        <v>-74.28571428571429</v>
-      </c>
-      <c r="AP3">
-        <v>-10.56768558951965</v>
+        <v>-46.89655172413793</v>
       </c>
       <c r="AQ3">
-        <v>-148.5714285714286</v>
+        <v>-46.89655172413793</v>
       </c>
     </row>
   </sheetData>
